--- a/Testing/Bug Report.xlsx
+++ b/Testing/Bug Report.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bangs\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bangs\Desktop\GitHub\book-store-management-system-ba\Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A633D20-4D3A-46D9-933B-D60A61696DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1A3C62-5B8A-4115-A380-B92DDAEFA1FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Simple Bug Report Template" sheetId="1" r:id="rId1"/>
@@ -140,9 +140,6 @@
     <t>Lê Thị Hằng</t>
   </si>
   <si>
-    <t>15/03/2026</t>
-  </si>
-  <si>
     <t>Không hiển thị thông báo khi không tìm thấy sản phẩm</t>
   </si>
   <si>
@@ -173,6 +170,9 @@
   </si>
   <si>
     <t>Liên quan TC-002, UC-009 (EX-01), FR-009</t>
+  </si>
+  <si>
+    <t>22/03/2026</t>
   </si>
 </sst>
 </file>
@@ -589,6 +589,7 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -596,6 +597,253 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="mm/dd/yy;@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -626,7 +874,329 @@
         <left style="thin">
           <color theme="0" tint="-0.249977111117893"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </right>
         <top style="thin">
           <color theme="0" tint="-0.249977111117893"/>
         </top>
@@ -755,7 +1325,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -778,6 +1348,27 @@
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="0" tint="-0.249977111117893"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="thin">
           <color theme="0" tint="-0.249977111117893"/>
         </left>
@@ -787,7 +1378,7 @@
         <top style="thin">
           <color theme="0" tint="-0.249977111117893"/>
         </top>
-        <bottom style="thin">
+        <bottom style="medium">
           <color theme="0" tint="-0.249977111117893"/>
         </bottom>
       </border>
@@ -816,597 +1407,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="mm/dd/yy;@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="medium">
-          <color theme="0" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1545,7 +1545,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7FE54C03-3649-1248-A4BA-0578B3EB9A73}" name="Table1" displayName="Table1" ref="B2:U32" totalsRowShown="0" headerRowDxfId="33" dataDxfId="9" headerRowBorderDxfId="32" tableBorderDxfId="31" totalsRowBorderDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7FE54C03-3649-1248-A4BA-0578B3EB9A73}" name="Table1" displayName="Table1" ref="B2:U32" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
   <autoFilter ref="B2:U32" xr:uid="{095C7E5B-8252-F741-A12E-5F50D45E743C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1569,26 +1569,26 @@
     <filterColumn colId="19" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{60DB6528-7C6F-3949-8DC5-39029C2B8FA9}" name="BUG ID" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{DBAAE93F-9BEF-7D4F-B744-E9172B23F1A6}" name="TITLE" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{F2308639-C083-2440-A774-5C1BA0C1C549}" name="REPORTED BY" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{35B302BC-E331-C84C-AC2F-408914E97D36}" name="DATE REPORTED" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{4747DC13-4CC3-FE47-BD01-EBE151C2885A}" name="SUMMARY" dataDxfId="25"/>
-    <tableColumn id="15" xr3:uid="{4D724BBC-C07C-B64B-9635-FFC079012231}" name="URL" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{46C8A186-CFD5-1A4D-9007-10EAF4DABC90}" name="SCREENSHOT" dataDxfId="23"/>
-    <tableColumn id="16" xr3:uid="{C8C5A442-59A6-7F47-912F-90E528C44DD0}" name="PLATFORM" dataDxfId="22"/>
-    <tableColumn id="17" xr3:uid="{A5486FF8-AB31-4345-BCB0-8D9DF0FD699A}" name="OPERATING SYSTEM" dataDxfId="21"/>
-    <tableColumn id="18" xr3:uid="{39C591F4-782F-CB4B-BF44-B4CCD11723A9}" name="BROWSER" dataDxfId="20"/>
-    <tableColumn id="19" xr3:uid="{88C11E58-C0F8-7343-95E5-7CE29CFDEE15}" name="STEPS TO REPRODUCE" dataDxfId="19"/>
-    <tableColumn id="20" xr3:uid="{8A5D5C17-B27D-7A42-B45A-2EC555DE51B0}" name="EXPECTED RESULT" dataDxfId="18"/>
-    <tableColumn id="21" xr3:uid="{1A7D220D-8A12-AF4D-A654-6078734D3606}" name="ACTUAL RESULT" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{08B2CD66-819F-B84D-B079-7DF6A94B2947}" name="DEFECT SEVERITY" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{B195CACC-E86E-934E-AA10-37C6D19CDBCE}" name="DEFECT PRIORITY" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{9CD17306-3FD2-2945-8DC6-DDA19A82BC10}" name="ASSIGNED TO" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{3DF5A60D-6098-CF4F-88D9-931EAD89B2F9}" name="STATUS" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{0F688ACD-44FE-C54D-98D5-A82F1B768F7D}" name="RESOLUTION" dataDxfId="12"/>
-    <tableColumn id="13" xr3:uid="{51D7F6E7-8FF2-4B4A-91C3-7701BD2B64BF}" name="DATE OF FIX" dataDxfId="11"/>
-    <tableColumn id="14" xr3:uid="{FC984278-8598-8C42-AD4C-1547465D297D}" name="NOTES" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{60DB6528-7C6F-3949-8DC5-39029C2B8FA9}" name="BUG ID" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{DBAAE93F-9BEF-7D4F-B744-E9172B23F1A6}" name="TITLE" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{F2308639-C083-2440-A774-5C1BA0C1C549}" name="REPORTED BY" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{35B302BC-E331-C84C-AC2F-408914E97D36}" name="DATE REPORTED" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{4747DC13-4CC3-FE47-BD01-EBE151C2885A}" name="SUMMARY" dataDxfId="24"/>
+    <tableColumn id="15" xr3:uid="{4D724BBC-C07C-B64B-9635-FFC079012231}" name="URL" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{46C8A186-CFD5-1A4D-9007-10EAF4DABC90}" name="SCREENSHOT" dataDxfId="22"/>
+    <tableColumn id="16" xr3:uid="{C8C5A442-59A6-7F47-912F-90E528C44DD0}" name="PLATFORM" dataDxfId="21"/>
+    <tableColumn id="17" xr3:uid="{A5486FF8-AB31-4345-BCB0-8D9DF0FD699A}" name="OPERATING SYSTEM" dataDxfId="20"/>
+    <tableColumn id="18" xr3:uid="{39C591F4-782F-CB4B-BF44-B4CCD11723A9}" name="BROWSER" dataDxfId="19"/>
+    <tableColumn id="19" xr3:uid="{88C11E58-C0F8-7343-95E5-7CE29CFDEE15}" name="STEPS TO REPRODUCE" dataDxfId="18"/>
+    <tableColumn id="20" xr3:uid="{8A5D5C17-B27D-7A42-B45A-2EC555DE51B0}" name="EXPECTED RESULT" dataDxfId="17"/>
+    <tableColumn id="21" xr3:uid="{1A7D220D-8A12-AF4D-A654-6078734D3606}" name="ACTUAL RESULT" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{08B2CD66-819F-B84D-B079-7DF6A94B2947}" name="DEFECT SEVERITY" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{B195CACC-E86E-934E-AA10-37C6D19CDBCE}" name="DEFECT PRIORITY" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{9CD17306-3FD2-2945-8DC6-DDA19A82BC10}" name="ASSIGNED TO" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{3DF5A60D-6098-CF4F-88D9-931EAD89B2F9}" name="STATUS" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{0F688ACD-44FE-C54D-98D5-A82F1B768F7D}" name="RESOLUTION" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{51D7F6E7-8FF2-4B4A-91C3-7701BD2B64BF}" name="DATE OF FIX" dataDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{FC984278-8598-8C42-AD4C-1547465D297D}" name="NOTES" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1992,38 +1992,38 @@
         <v>29</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="26" t="s">
         <v>33</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>34</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>1</v>
@@ -2038,7 +2038,7 @@
       <c r="S3" s="7"/>
       <c r="T3" s="11"/>
       <c r="U3" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="2:21" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
